--- a/data/trans_camb/P6902-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 59,1</t>
+          <t>-10,8; 58,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 25,84</t>
+          <t>-27,82; 24,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 64,18</t>
+          <t>-46,47; 63,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 46,01</t>
+          <t>-26,82; 49,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 53,35</t>
+          <t>-20,92; 51,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 61,6</t>
+          <t>3,68; 62,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 44,06</t>
+          <t>-3,89; 45,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 27,02</t>
+          <t>-15,9; 27,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 56,24</t>
+          <t>0,89; 55,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 199,98</t>
+          <t>-20,22; 191,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 84,71</t>
+          <t>-63,44; 85,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 197,5</t>
+          <t>-100,0; 188,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 145,73</t>
+          <t>-45,16; 150,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 175,22</t>
+          <t>-33,21; 170,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 217,04</t>
+          <t>8,71; 239,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 128,03</t>
+          <t>-8,76; 128,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 79,42</t>
+          <t>-33,33; 81,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 166,29</t>
+          <t>8,11; 161,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 23,82</t>
+          <t>-4,79; 23,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 6,1</t>
+          <t>-20,37; 6,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,82; 47,21</t>
+          <t>12,17; 47,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 14,52</t>
+          <t>-18,17; 13,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 19,83</t>
+          <t>-15,52; 19,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 30,44</t>
+          <t>-4,77; 29,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 16,53</t>
+          <t>-5,18; 15,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 8,02</t>
+          <t>-14,85; 6,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 35,55</t>
+          <t>10,64; 35,76</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 63,25</t>
+          <t>-9,56; 60,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 17,26</t>
+          <t>-42,33; 18,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 128,13</t>
+          <t>26,75; 122,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 30,98</t>
+          <t>-29,97; 27,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 41,41</t>
+          <t>-25,41; 40,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 63,94</t>
+          <t>-5,82; 61,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 37,42</t>
+          <t>-10,21; 37,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 18,49</t>
+          <t>-28,43; 15,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,78; 80,69</t>
+          <t>20,25; 82,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 14,76</t>
+          <t>-10,87; 15,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 4,75</t>
+          <t>-20,31; 6,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 21,37</t>
+          <t>-6,64; 21,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 26,94</t>
+          <t>-5,29; 27,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 29,89</t>
+          <t>-5,04; 30,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 26,3</t>
+          <t>-3,62; 27,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 16,45</t>
+          <t>-6,3; 15,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 9,87</t>
+          <t>-11,29; 9,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 19,05</t>
+          <t>-1,81; 19,13</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 35,75</t>
+          <t>-20,79; 40,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 13,09</t>
+          <t>-38,56; 15,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 53,62</t>
+          <t>-13,04; 54,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 68,0</t>
+          <t>-9,06; 64,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 70,12</t>
+          <t>-8,38; 76,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 65,55</t>
+          <t>-5,78; 70,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 36,91</t>
+          <t>-11,98; 37,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 23,39</t>
+          <t>-21,33; 22,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 45,12</t>
+          <t>-3,41; 44,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 7,38</t>
+          <t>-23,13; 5,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 18,91</t>
+          <t>-11,28; 17,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 29,62</t>
+          <t>1,96; 28,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 22,43</t>
+          <t>-21,14; 23,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 27,3</t>
+          <t>-14,12; 24,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 23,26</t>
+          <t>-34,73; 24,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 8,35</t>
+          <t>-16,32; 7,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 17,49</t>
+          <t>-7,02; 17,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 22,72</t>
+          <t>-13,58; 21,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 18,36</t>
+          <t>-43,41; 14,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 49,69</t>
+          <t>-21,06; 43,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 79,58</t>
+          <t>4,52; 74,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 62,73</t>
+          <t>-34,62; 63,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 72,9</t>
+          <t>-24,13; 63,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 55,56</t>
+          <t>-50,42; 58,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 20,3</t>
+          <t>-31,64; 19,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 43,84</t>
+          <t>-12,31; 44,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 53,27</t>
+          <t>-23,3; 51,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 33,38</t>
+          <t>-5,47; 33,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 45,21</t>
+          <t>3,63; 45,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,21; 51,17</t>
+          <t>13,38; 47,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 59,09</t>
+          <t>-8,58; 57,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 55,61</t>
+          <t>-4,71; 58,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 54,88</t>
+          <t>0,54; 54,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 36,61</t>
+          <t>3,73; 38,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,42; 43,71</t>
+          <t>9,49; 43,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,99; 46,28</t>
+          <t>17,73; 46,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 158,65</t>
+          <t>-14,19; 163,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,69; 215,24</t>
+          <t>8,79; 235,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31,72; 270,1</t>
+          <t>31,21; 236,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 417,82</t>
+          <t>-15,77; 373,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 378,1</t>
+          <t>-10,97; 356,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,34; 374,11</t>
+          <t>0,1; 374,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,4; 165,88</t>
+          <t>8,47; 170,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23,04; 211,74</t>
+          <t>25,8; 190,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46,59; 220,7</t>
+          <t>41,39; 212,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,75</t>
+          <t>-3,74; 10,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 6,81</t>
+          <t>-7,96; 6,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,83; 25,95</t>
+          <t>11,14; 25,33</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 15,3</t>
+          <t>-3,92; 16,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 18,09</t>
+          <t>-0,21; 19,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 19,12</t>
+          <t>-9,75; 18,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 10,81</t>
+          <t>-0,8; 11,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,6</t>
+          <t>-1,51; 9,97</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,85; 21,39</t>
+          <t>5,18; 21,17</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 25,81</t>
+          <t>-8,34; 25,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 16,88</t>
+          <t>-17,57; 16,45</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25,51; 64,31</t>
+          <t>23,74; 63,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 33,11</t>
+          <t>-6,75; 34,81</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 39,78</t>
+          <t>-0,39; 41,95</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 40,44</t>
+          <t>-17,14; 38,56</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 25,55</t>
+          <t>-1,52; 25,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 22,4</t>
+          <t>-3,23; 22,95</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,16; 49,41</t>
+          <t>11,51; 48,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6902-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,91</t>
+          <t>-4,37</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,3</t>
+          <t>38,32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,46</t>
+          <t>25,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 58,81</t>
+          <t>-8,01; 59,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 24,17</t>
+          <t>-32,16; 24,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,47; 63,11</t>
+          <t>-42,37; 60,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 49,48</t>
+          <t>-29,56; 43,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 51,36</t>
+          <t>-20,2; 51,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 62,73</t>
+          <t>5,11; 62,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 45,04</t>
+          <t>-6,05; 43,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 27,75</t>
+          <t>-18,32; 25,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 55,68</t>
+          <t>-7,72; 51,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>-11,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 191,71</t>
+          <t>-16,4; 206,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 85,85</t>
+          <t>-71,26; 85,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,27</t>
+          <t>-100,0; 159,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 150,92</t>
+          <t>-52,34; 133,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 170,36</t>
+          <t>-31,9; 163,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 239,01</t>
+          <t>9,88; 214,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 128,92</t>
+          <t>-11,11; 135,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 81,17</t>
+          <t>-39,29; 76,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 161,7</t>
+          <t>-14,74; 150,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30,49</t>
+          <t>32,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,24</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24,34</t>
+          <t>24,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 23,13</t>
+          <t>-4,53; 24,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 6,56</t>
+          <t>-20,72; 7,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 47,32</t>
+          <t>15,08; 46,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 13,29</t>
+          <t>-19,91; 14,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 19,92</t>
+          <t>-14,15; 21,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 29,12</t>
+          <t>-4,12; 30,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 15,99</t>
+          <t>-5,21; 15,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 6,88</t>
+          <t>-14,26; 8,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 35,76</t>
+          <t>11,48; 36,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 60,58</t>
+          <t>-9,32; 61,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 18,07</t>
+          <t>-41,86; 20,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 122,46</t>
+          <t>32,77; 134,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 27,44</t>
+          <t>-31,07; 29,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 40,33</t>
+          <t>-22,78; 45,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 61,93</t>
+          <t>-6,27; 64,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 37,04</t>
+          <t>-9,84; 36,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 15,51</t>
+          <t>-27,22; 19,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,25; 82,81</t>
+          <t>23,96; 82,67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,13</t>
+          <t>9,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 15,8</t>
+          <t>-13,58; 14,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 6,21</t>
+          <t>-21,21; 5,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 21,42</t>
+          <t>-6,4; 21,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 27,57</t>
+          <t>-5,98; 27,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 30,51</t>
+          <t>-3,87; 28,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 27,23</t>
+          <t>-5,13; 24,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 15,57</t>
+          <t>-5,27; 15,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 9,53</t>
+          <t>-11,25; 9,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 19,13</t>
+          <t>-1,52; 18,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 40,36</t>
+          <t>-25,18; 36,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 15,47</t>
+          <t>-41,67; 14,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 54,36</t>
+          <t>-11,51; 54,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 64,75</t>
+          <t>-8,66; 69,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 76,96</t>
+          <t>-6,43; 72,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 70,41</t>
+          <t>-9,15; 63,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 37,04</t>
+          <t>-10,7; 37,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 22,5</t>
+          <t>-21,1; 22,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 44,57</t>
+          <t>-2,37; 44,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>15,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>20,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>18,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 5,5</t>
+          <t>-23,44; 6,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 17,43</t>
+          <t>-9,11; 20,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 28,23</t>
+          <t>2,52; 30,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 23,58</t>
+          <t>-21,44; 25,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 24,45</t>
+          <t>-15,51; 27,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 24,54</t>
+          <t>4,21; 37,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 7,81</t>
+          <t>-16,67; 8,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 17,4</t>
+          <t>-6,84; 17,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 21,93</t>
+          <t>9,14; 29,22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 14,6</t>
+          <t>-44,07; 17,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 43,72</t>
+          <t>-17,62; 50,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 74,42</t>
+          <t>5,11; 78,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 63,24</t>
+          <t>-35,74; 67,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 63,72</t>
+          <t>-25,37; 75,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 58,53</t>
+          <t>7,38; 114,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 19,11</t>
+          <t>-32,48; 18,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 44,1</t>
+          <t>-13,05; 43,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 51,77</t>
+          <t>17,06; 73,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33,25</t>
+          <t>33,49</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,32</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>33,22</t>
+          <t>32,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 33,47</t>
+          <t>-4,04; 35,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 45,78</t>
+          <t>0,47; 42,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,38; 47,71</t>
+          <t>15,28; 50,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 57,11</t>
+          <t>-8,01; 57,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 58,45</t>
+          <t>-7,53; 56,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 54,01</t>
+          <t>-0,23; 53,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 38,48</t>
+          <t>2,24; 37,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 43,27</t>
+          <t>9,69; 41,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,73; 46,37</t>
+          <t>18,37; 45,17</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110,21%</t>
+          <t>111,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>105,31%</t>
+          <t>104,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 163,37</t>
+          <t>-12,75; 177,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,79; 235,28</t>
+          <t>2,07; 217,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31,21; 236,37</t>
+          <t>33,68; 282,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 373,45</t>
+          <t>-13,85; 405,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 356,61</t>
+          <t>-13,63; 378,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,1; 374,93</t>
+          <t>-0,38; 371,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,47; 170,24</t>
+          <t>4,04; 170,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>25,8; 190,78</t>
+          <t>24,56; 184,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41,39; 212,95</t>
+          <t>43,86; 213,85</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15,22</t>
+          <t>18,41</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 10,52</t>
+          <t>-3,76; 10,4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,68</t>
+          <t>-7,6; 7,24</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,14; 25,33</t>
+          <t>10,54; 24,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 16,13</t>
+          <t>-4,02; 15,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 19,33</t>
+          <t>-0,47; 18,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 18,62</t>
+          <t>7,91; 23,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 11,08</t>
+          <t>-0,27; 10,73</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 9,97</t>
+          <t>-2,02; 10,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,18; 21,17</t>
+          <t>13,33; 23,63</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 25,52</t>
+          <t>-8,31; 25,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 16,45</t>
+          <t>-16,43; 17,69</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23,74; 63,93</t>
+          <t>21,72; 61,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 34,81</t>
+          <t>-7,05; 34,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 41,95</t>
+          <t>-0,81; 40,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 38,56</t>
+          <t>13,97; 51,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 25,82</t>
+          <t>-0,8; 25,35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 22,95</t>
+          <t>-4,13; 23,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,51; 48,91</t>
+          <t>26,93; 54,31</t>
         </is>
       </c>
     </row>
